--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ТРАКИЙСКИ УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС/ТРАКИЙСКИ УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ТРАКИЙСКИ УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС/ТРАКИЙСКИ УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС.xlsx
@@ -148,7 +148,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -819,7 +819,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="7">
-        <v>1.5133</v>
+        <v>1.513261</v>
       </c>
       <c r="E10" s="6">
         <v>139.22</v>
@@ -839,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="7">
-        <v>1.72</v>
+        <v>1.720036</v>
       </c>
       <c r="E11" s="6">
         <v>114.52</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ТРАКИЙСКИ УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС/ТРАКИЙСКИ УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ТРАКИЙСКИ УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС/ТРАКИЙСКИ УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="43">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -539,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -552,13 +555,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -601,186 +604,201 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2">
         <v>30</v>
       </c>
       <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2">
+        <v>1.401</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J2">
+        <v>45.6</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L2" s="1">
+        <v>46.5</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="H2">
-        <v>1.52</v>
-      </c>
-      <c r="I2" s="1">
-        <v>45.6</v>
-      </c>
-      <c r="J2">
-        <v>1.55</v>
-      </c>
-      <c r="K2" s="1">
-        <v>46.5</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="F3">
+        <v>66.583</v>
+      </c>
+      <c r="G3" t="s">
         <v>28</v>
       </c>
-      <c r="M2">
+      <c r="H3">
+        <v>1.674</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.72</v>
+      </c>
+      <c r="J3">
+        <v>114.52276</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L3" s="1">
+        <v>116.52025</v>
+      </c>
+      <c r="M3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="O3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
         <v>26</v>
-      </c>
-      <c r="F3">
-        <v>66.58</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3">
-        <v>1.72</v>
-      </c>
-      <c r="I3" s="1">
-        <v>114.52</v>
-      </c>
-      <c r="J3">
-        <v>1.75</v>
-      </c>
-      <c r="K3" s="1">
-        <v>116.52</v>
-      </c>
-      <c r="L3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
       </c>
       <c r="F4">
         <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H4">
+        <v>1.459</v>
+      </c>
+      <c r="I4" s="1">
         <v>1.51</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>48.32</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>1.54</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>49.28</v>
       </c>
-      <c r="L4" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4">
+      <c r="M4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5">
         <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5">
+        <v>1.459</v>
+      </c>
+      <c r="I5" s="1">
         <v>1.51</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>45.3</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>1.54</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>46.2</v>
       </c>
-      <c r="L5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5">
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -788,29 +806,29 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="6">
         <v>92</v>
@@ -828,18 +846,18 @@
         <v>141.98</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" s="6">
-        <v>66.58</v>
+        <v>66.583</v>
       </c>
       <c r="C11" s="6">
         <v>1</v>
       </c>
       <c r="D11" s="7">
-        <v>1.720036</v>
+        <v>1.72</v>
       </c>
       <c r="E11" s="6">
         <v>114.52</v>
@@ -848,12 +866,12 @@
         <v>116.52</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15">
       <c r="A12" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="9">
-        <v>158.58</v>
+        <v>158.583</v>
       </c>
       <c r="C12" s="9">
         <v>4</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ТРАКИЙСКИ УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС/ТРАКИЙСКИ УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ТРАКИЙСКИ УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС/ТРАКИЙСКИ УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="42">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -150,8 +147,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -244,10 +241,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -542,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -555,13 +552,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -604,201 +601,186 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2">
         <v>30</v>
       </c>
       <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2">
+        <v>1.52</v>
+      </c>
+      <c r="I2" s="1">
+        <v>45.6</v>
+      </c>
+      <c r="J2">
+        <v>1.55</v>
+      </c>
+      <c r="K2" s="1">
+        <v>46.5</v>
+      </c>
+      <c r="L2" t="s">
         <v>28</v>
       </c>
-      <c r="H2">
-        <v>1.401</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J2">
-        <v>45.6</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L2" s="1">
-        <v>46.5</v>
-      </c>
-      <c r="M2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3">
         <v>66.583</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H3">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I3" s="1">
-        <v>1.72</v>
+        <v>114.523</v>
       </c>
       <c r="J3">
-        <v>114.52276</v>
+        <v>1.75</v>
       </c>
       <c r="K3" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L3" s="1">
-        <v>116.52025</v>
-      </c>
-      <c r="M3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3">
+        <v>116.52</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
         <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
       </c>
       <c r="F4">
         <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H4">
-        <v>1.459</v>
+        <v>1.51</v>
       </c>
       <c r="I4" s="1">
-        <v>1.51</v>
+        <v>48.32</v>
       </c>
       <c r="J4">
-        <v>48.32</v>
+        <v>1.54</v>
       </c>
       <c r="K4" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L4" s="1">
         <v>49.28</v>
       </c>
-      <c r="M4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4">
+      <c r="L4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5">
         <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H5">
-        <v>1.459</v>
+        <v>1.51</v>
       </c>
       <c r="I5" s="1">
-        <v>1.51</v>
+        <v>45.3</v>
       </c>
       <c r="J5">
-        <v>45.3</v>
+        <v>1.54</v>
       </c>
       <c r="K5" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L5" s="1">
         <v>46.2</v>
       </c>
-      <c r="M5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5">
+      <c r="L5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
+      <c r="N5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -806,69 +788,69 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E9" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="6">
         <v>92</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
         <v>3</v>
       </c>
       <c r="D10" s="7">
-        <v>1.513261</v>
-      </c>
-      <c r="E10" s="6">
+        <v>1.513</v>
+      </c>
+      <c r="E10" s="7">
         <v>139.22</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <v>141.98</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="A11" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="6">
         <v>66.583</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="7">
         <v>1</v>
       </c>
       <c r="D11" s="7">
         <v>1.72</v>
       </c>
-      <c r="E11" s="6">
-        <v>114.52</v>
-      </c>
-      <c r="F11" s="6">
+      <c r="E11" s="7">
+        <v>114.523</v>
+      </c>
+      <c r="F11" s="7">
         <v>116.52</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:14">
       <c r="A12" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="9">
         <v>158.583</v>
@@ -878,7 +860,7 @@
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="9">
-        <v>253.74</v>
+        <v>253.743</v>
       </c>
       <c r="F12" s="9">
         <v>258.5</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ТРАКИЙСКИ УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС/ТРАКИЙСКИ УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ТРАКИЙСКИ УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС/ТРАКИЙСКИ УНИВЕРСИТЕТ % 4 - АКАДЕМИЧЕН ТЕХНОЛОГИЧЕН КОМПЛЕКС.xlsx
@@ -616,10 +616,10 @@
         <v>25</v>
       </c>
       <c r="H2" s="1">
-        <v>1.409</v>
+        <v>1.51</v>
       </c>
       <c r="I2" s="1">
-        <v>42.27</v>
+        <v>45.3</v>
       </c>
       <c r="J2" s="1">
         <v>1.54</v>
@@ -660,10 +660,10 @@
         <v>25</v>
       </c>
       <c r="H3" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I3" s="1">
-        <v>109.38</v>
+        <v>117.216</v>
       </c>
       <c r="J3" s="1">
         <v>1.84</v>
@@ -704,10 +704,10 @@
         <v>25</v>
       </c>
       <c r="H4" s="1">
-        <v>1.459</v>
+        <v>1.56</v>
       </c>
       <c r="I4" s="1">
-        <v>43.77</v>
+        <v>46.8</v>
       </c>
       <c r="J4" s="1">
         <v>1.59</v>
@@ -766,10 +766,10 @@
         <v>1</v>
       </c>
       <c r="D9" s="8">
-        <v>1.68901</v>
+        <v>1.81001</v>
       </c>
       <c r="E9" s="6">
-        <v>109.38</v>
+        <v>117.22</v>
       </c>
       <c r="F9" s="6">
         <v>119.16</v>
@@ -786,10 +786,10 @@
         <v>2</v>
       </c>
       <c r="D10" s="8">
-        <v>1.434</v>
+        <v>1.535</v>
       </c>
       <c r="E10" s="6">
-        <v>86.04000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F10" s="6">
         <v>93.90000000000001</v>
@@ -807,7 +807,7 @@
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="10">
-        <v>195.42</v>
+        <v>209.32</v>
       </c>
       <c r="F11" s="10">
         <v>213.06</v>
